--- a/data/gravel/Giant Revolt pro (short) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (short) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60595B95-5761-7448-916F-A45DBD4330A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D57975-2CCD-D849-9D6D-6776280682BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1780" yWindow="500" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33380" yWindow="-17820" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2058,7 +2058,7 @@
         <v>121</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C16:C18" si="3">VALUE(LEFT(J18,2))</f>
+        <f t="shared" ref="C18" si="3">VALUE(LEFT(J18,2))</f>
         <v>80</v>
       </c>
       <c r="D18" s="5">

--- a/data/gravel/Giant Revolt pro (short) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (short) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D57975-2CCD-D849-9D6D-6776280682BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFB48F3-0F1E-B642-ACF2-CD7C7032B81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33380" yWindow="-17820" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13500" yWindow="640" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="134">
   <si>
     <t>brand</t>
   </si>
@@ -282,12 +282,6 @@
   </si>
   <si>
     <t>rigid</t>
-  </si>
-  <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
   </si>
   <si>
     <r>
@@ -1125,13 +1119,22 @@
     <t>yes</t>
   </si>
   <si>
-    <t>a8:h33</t>
-  </si>
-  <si>
     <t>Revolt Advanced Pro (short)</t>
   </si>
   <si>
-    <t>flip</t>
+    <t>a8:h31</t>
+  </si>
+  <si>
+    <t>https://www.giant-bicycles.com/us/revolt-advanced-pro-1</t>
+  </si>
+  <si>
+    <t>https://images2.giant-bicycles.com/b_white%2Cc_pad%2Ch_850%2Cq_80/nu50syqftgvwjxg8dlia/MY25RevoltAdvancedPro1_ColorAMeteorStorm.jpg</t>
+  </si>
+  <si>
+    <t>± 10</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -1523,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1542,7 +1545,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -1565,13 +1568,21 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>8</v>
@@ -1597,7 +1608,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>8</v>
@@ -1618,22 +1629,22 @@
         <v>13</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1641,7 +1652,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C9" s="5">
         <v>430</v>
@@ -1685,7 +1696,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C10" s="5">
         <v>74</v>
@@ -1706,22 +1717,22 @@
         <v>73</v>
       </c>
       <c r="J10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="N10" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1729,7 +1740,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C11" s="5">
         <v>540</v>
@@ -1773,7 +1784,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C12" s="5">
         <v>125</v>
@@ -1817,7 +1828,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C13" s="5">
         <v>70</v>
@@ -1838,22 +1849,22 @@
         <v>72</v>
       </c>
       <c r="J13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="M13" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="L13" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="N13" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1861,7 +1872,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C14" s="5">
         <v>50</v>
@@ -1905,7 +1916,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C15" s="5">
         <f>VALUE(LEFT(J15,2))</f>
@@ -1932,22 +1943,22 @@
         <v>65</v>
       </c>
       <c r="J15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="M15" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="L15" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="N15" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1955,7 +1966,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" s="5">
         <f>VALUE(LEFT(J16,4))</f>
@@ -1982,22 +1993,22 @@
         <v>1056</v>
       </c>
       <c r="J16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="M16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="N16" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="O16" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -2005,7 +2016,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C17" s="5">
         <f>VALUE(LEFT(J17,3))</f>
@@ -2032,22 +2043,22 @@
         <v>425</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -2055,7 +2066,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" s="5">
         <f t="shared" ref="C18" si="3">VALUE(LEFT(J18,2))</f>
@@ -2082,22 +2093,22 @@
         <v>80</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -2105,7 +2116,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C19" s="5">
         <v>556</v>
@@ -2149,7 +2160,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C20" s="5">
         <v>381</v>
@@ -2193,7 +2204,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C21" s="5">
         <f>VALUE(LEFT(J21,3))</f>
@@ -2220,22 +2231,22 @@
         <v>807</v>
       </c>
       <c r="J21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L21" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="M21" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="N21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="O21" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -2243,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C22" s="5">
         <v>420</v>
@@ -2287,7 +2298,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="5">
         <v>50</v>
@@ -2331,7 +2342,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C24" s="5">
         <v>170</v>
@@ -2487,28 +2498,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <f>C32</f>
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D30">
-        <f>AVERAGE(D32,C33)</f>
-        <v>157.5</v>
+        <v>159</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30:H30" si="10">AVERAGE(E32,D33)</f>
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F30">
-        <f t="shared" si="10"/>
-        <v>177.5</v>
+        <v>174</v>
       </c>
       <c r="G30">
-        <f t="shared" si="10"/>
-        <v>182.5</v>
+        <v>179</v>
       </c>
       <c r="H30">
-        <f t="shared" si="10"/>
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -2519,336 +2524,290 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <f>D30</f>
-        <v>157.5</v>
+        <v>156</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:G31" si="11">E30</f>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E31">
-        <f t="shared" si="11"/>
-        <v>177.5</v>
+        <v>181</v>
       </c>
       <c r="F31">
-        <f t="shared" si="11"/>
-        <v>182.5</v>
+        <v>186</v>
       </c>
       <c r="G31">
-        <f t="shared" si="11"/>
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H31">
-        <f>H33</f>
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32">
-        <v>155</v>
-      </c>
-      <c r="D32">
-        <v>159</v>
-      </c>
-      <c r="E32">
-        <v>169</v>
-      </c>
-      <c r="F32">
-        <v>174</v>
-      </c>
-      <c r="G32">
-        <v>179</v>
-      </c>
-      <c r="H32">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33">
-        <v>156</v>
-      </c>
-      <c r="D33">
-        <v>171</v>
-      </c>
-      <c r="E33">
-        <v>181</v>
-      </c>
-      <c r="F33">
-        <v>186</v>
-      </c>
-      <c r="G33">
-        <v>191</v>
-      </c>
-      <c r="H33">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="B40">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="B46">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="B47">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48">
-        <v>142</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="B50">
+        <v>30.9</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52">
-        <v>30.9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>60</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>129</v>
+        <v>65</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>66</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="B68">
+        <v>2300</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>70</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>129</v>
+        <v>72</v>
+      </c>
+      <c r="B69">
+        <v>5000</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
-      </c>
-      <c r="B70">
-        <v>2300</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
         <v>74</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Giant Revolt pro (short) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (short) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFB48F3-0F1E-B642-ACF2-CD7C7032B81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126FB4C9-8736-4440-A585-8BE2BE87E5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13500" yWindow="640" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
   <si>
     <t>brand</t>
   </si>
@@ -1135,6 +1135,12 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dajia, Taichung, Taiwan</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2810,6 +2816,14 @@
         <v>133</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Giant Revolt pro (short) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (short) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126FB4C9-8736-4440-A585-8BE2BE87E5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC0B62C-F061-4947-86BB-4874D419FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="142">
   <si>
     <t>brand</t>
   </si>
@@ -1141,6 +1141,24 @@
   </si>
   <si>
     <t>Dajia, Taichung, Taiwan</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2655,172 +2673,202 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="1"/>
+        <v>136</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50">
-        <v>30.9</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>57</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>30.9</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>66</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>127</v>
+        <v>64</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B68">
-        <v>2300</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B69">
-        <v>5000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>134</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>135</v>
       </c>
     </row>
